--- a/output/semivariogram-models.xlsx
+++ b/output/semivariogram-models.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -455,7 +455,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>m%</t>
+          <t>CTC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -464,22 +464,22 @@
         </is>
       </c>
       <c r="E3">
-        <v>0.3989</v>
+        <v>0.0056</v>
       </c>
       <c r="F3">
-        <v>0.6781</v>
+        <v>0.0343</v>
       </c>
       <c r="G3">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H3">
-        <v>0.588261318389618</v>
+        <v>0.163265306122449</v>
       </c>
       <c r="I3">
-        <v>360178.4933</v>
+        <v>715.0113</v>
       </c>
       <c r="J3">
-        <v>0.8599796044645488</v>
+        <v>0.8540235753697586</v>
       </c>
     </row>
     <row r="4">
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>m%</t>
+          <t>H+Al</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -502,22 +502,22 @@
         </is>
       </c>
       <c r="E4">
-        <v>0.3989</v>
+        <v>0.0218</v>
       </c>
       <c r="F4">
-        <v>0.6781</v>
+        <v>0.0537</v>
       </c>
       <c r="G4">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H4">
-        <v>0.588261318389618</v>
+        <v>0.4059590316573557</v>
       </c>
       <c r="I4">
-        <v>360178.4933</v>
+        <v>2867.6611</v>
       </c>
       <c r="J4">
-        <v>0.8599796044645488</v>
+        <v>0.8038674943138583</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +531,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TCH</t>
+          <t>K</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -540,22 +540,22 @@
         </is>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="F5">
-        <v>539.082</v>
+        <v>0.1874</v>
       </c>
       <c r="G5">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.4002134471718249</v>
       </c>
       <c r="I5">
-        <v>399559536791.8976</v>
+        <v>34477.6578</v>
       </c>
       <c r="J5">
-        <v>0.9608188629714224</v>
+        <v>0.8937073847377305</v>
       </c>
     </row>
     <row r="6">
@@ -564,36 +564,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>POT</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ca</t>
+          <t>m%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sph</t>
+          <t>Exp</t>
         </is>
       </c>
       <c r="E6">
-        <v>0.0827</v>
+        <v>0.3989</v>
       </c>
       <c r="F6">
-        <v>0.1381</v>
+        <v>0.6781</v>
       </c>
       <c r="G6">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H6">
-        <v>0.5988414192614048</v>
+        <v>0.588261318389618</v>
       </c>
       <c r="I6">
-        <v>92226.60709999999</v>
+        <v>360178.4933</v>
       </c>
       <c r="J6">
-        <v>0.3505038379899719</v>
+        <v>0.8599796044645488</v>
       </c>
     </row>
     <row r="7">
@@ -602,12 +602,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>POT</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>m%</t>
+          <t>Mg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -616,22 +616,22 @@
         </is>
       </c>
       <c r="E7">
-        <v>0.5491</v>
+        <v>0.0489</v>
       </c>
       <c r="F7">
-        <v>1.0464</v>
+        <v>0.1</v>
       </c>
       <c r="G7">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="H7">
-        <v>0.5247515290519879</v>
+        <v>0.489</v>
       </c>
       <c r="I7">
-        <v>3978503.3091</v>
+        <v>16739.7449</v>
       </c>
       <c r="J7">
-        <v>0.856099824277081</v>
+        <v>0.7238174534818483</v>
       </c>
     </row>
     <row r="8">
@@ -640,36 +640,2734 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>POT</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Gau</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>0.0238</v>
+      </c>
+      <c r="F8">
+        <v>0.0434</v>
+      </c>
+      <c r="G8">
+        <v>0.01</v>
+      </c>
+      <c r="H8">
+        <v>0.5483870967741936</v>
+      </c>
+      <c r="I8">
+        <v>439824.7913</v>
+      </c>
+      <c r="J8">
+        <v>0.9536034746581896</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>2016</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>0.1035</v>
+      </c>
+      <c r="F9">
+        <v>0.1943</v>
+      </c>
+      <c r="G9">
+        <v>0.02</v>
+      </c>
+      <c r="H9">
+        <v>0.532681420483788</v>
+      </c>
+      <c r="I9">
+        <v>101835.1919</v>
+      </c>
+      <c r="J9">
+        <v>0.720647593391613</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>2016</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>0.002</v>
+      </c>
+      <c r="F10">
+        <v>0.005</v>
+      </c>
+      <c r="G10">
+        <v>0.02</v>
+      </c>
+      <c r="H10">
+        <v>0.4</v>
+      </c>
+      <c r="I10">
+        <v>16.1664</v>
+      </c>
+      <c r="J10">
+        <v>0.8673352529533246</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>2016</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E11">
+        <v>0.1596</v>
+      </c>
+      <c r="F11">
+        <v>0.2499</v>
+      </c>
+      <c r="G11">
+        <v>0.03</v>
+      </c>
+      <c r="H11">
+        <v>0.6386554621848739</v>
+      </c>
+      <c r="I11">
+        <v>160260.0189</v>
+      </c>
+      <c r="J11">
+        <v>0.8379031633463351</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>2016</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>0.0429</v>
+      </c>
+      <c r="F12">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="G12">
+        <v>0.02</v>
+      </c>
+      <c r="H12">
+        <v>0.4902857142857143</v>
+      </c>
+      <c r="I12">
+        <v>3793.6373</v>
+      </c>
+      <c r="J12">
+        <v>0.8815614029705797</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>2016</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>TCH</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Exp</t>
-        </is>
-      </c>
-      <c r="E8">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E13">
         <v>0</v>
       </c>
-      <c r="F8">
+      <c r="F13">
+        <v>539.082</v>
+      </c>
+      <c r="G13">
+        <v>0.04</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>399559536791.8976</v>
+      </c>
+      <c r="J13">
+        <v>0.9608188629714224</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>2016</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>V%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E14">
+        <v>0.0221</v>
+      </c>
+      <c r="F14">
+        <v>0.0332</v>
+      </c>
+      <c r="G14">
+        <v>0.12</v>
+      </c>
+      <c r="H14">
+        <v>0.6656626506024097</v>
+      </c>
+      <c r="I14">
+        <v>1813.8488</v>
+      </c>
+      <c r="J14">
+        <v>0.7753413642587028</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>2016</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ca</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E15">
+        <v>0.0827</v>
+      </c>
+      <c r="F15">
+        <v>0.1381</v>
+      </c>
+      <c r="G15">
+        <v>0.02</v>
+      </c>
+      <c r="H15">
+        <v>0.5988414192614048</v>
+      </c>
+      <c r="I15">
+        <v>92226.60709999999</v>
+      </c>
+      <c r="J15">
+        <v>0.3505038379899719</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>2016</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CTC</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E16">
+        <v>0.0207</v>
+      </c>
+      <c r="F16">
+        <v>0.0483</v>
+      </c>
+      <c r="G16">
+        <v>0.03</v>
+      </c>
+      <c r="H16">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="I16">
+        <v>5300.458</v>
+      </c>
+      <c r="J16">
+        <v>0.8326769337678949</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>2016</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>H+Al</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E17">
+        <v>0.0377</v>
+      </c>
+      <c r="F17">
+        <v>0.06759999999999999</v>
+      </c>
+      <c r="G17">
+        <v>0.03</v>
+      </c>
+      <c r="H17">
+        <v>0.5576923076923077</v>
+      </c>
+      <c r="I17">
+        <v>6624.2467</v>
+      </c>
+      <c r="J17">
+        <v>0.9559687236488932</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>2016</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E18">
+        <v>0.0556</v>
+      </c>
+      <c r="F18">
+        <v>0.198</v>
+      </c>
+      <c r="G18">
+        <v>0.04</v>
+      </c>
+      <c r="H18">
+        <v>0.2808080808080808</v>
+      </c>
+      <c r="I18">
+        <v>213131.568</v>
+      </c>
+      <c r="J18">
+        <v>0.7287189671812222</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>2016</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>m%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E19">
+        <v>0.5491</v>
+      </c>
+      <c r="F19">
+        <v>1.0464</v>
+      </c>
+      <c r="G19">
+        <v>0.04</v>
+      </c>
+      <c r="H19">
+        <v>0.5247515290519879</v>
+      </c>
+      <c r="I19">
+        <v>3978503.3091</v>
+      </c>
+      <c r="J19">
+        <v>0.856099824277081</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>2016</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mg</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E20">
+        <v>0.0721</v>
+      </c>
+      <c r="F20">
+        <v>0.134</v>
+      </c>
+      <c r="G20">
+        <v>0.03</v>
+      </c>
+      <c r="H20">
+        <v>0.5380597014925372</v>
+      </c>
+      <c r="I20">
+        <v>50500.9792</v>
+      </c>
+      <c r="J20">
+        <v>0.767702131883519</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>2016</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E21">
+        <v>0.0184</v>
+      </c>
+      <c r="F21">
+        <v>0.0459</v>
+      </c>
+      <c r="G21">
+        <v>0.04</v>
+      </c>
+      <c r="H21">
+        <v>0.4008714596949891</v>
+      </c>
+      <c r="I21">
+        <v>1037.6595</v>
+      </c>
+      <c r="J21">
+        <v>0.970101475431462</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>2016</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0.1421</v>
+      </c>
+      <c r="G22">
+        <v>0.01</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>41145.4356</v>
+      </c>
+      <c r="J22">
+        <v>0.819252145747561</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>2016</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E23">
+        <v>0.0022</v>
+      </c>
+      <c r="F23">
+        <v>0.0059</v>
+      </c>
+      <c r="G23">
+        <v>0.02</v>
+      </c>
+      <c r="H23">
+        <v>0.3728813559322034</v>
+      </c>
+      <c r="I23">
+        <v>41.856</v>
+      </c>
+      <c r="J23">
+        <v>0.7835443966469006</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>2016</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E24">
+        <v>0.1056</v>
+      </c>
+      <c r="F24">
+        <v>0.2686</v>
+      </c>
+      <c r="G24">
+        <v>0.02</v>
+      </c>
+      <c r="H24">
+        <v>0.3931496649292629</v>
+      </c>
+      <c r="I24">
+        <v>50664.1094</v>
+      </c>
+      <c r="J24">
+        <v>0.8841353028250027</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>2016</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E25">
+        <v>0.0742</v>
+      </c>
+      <c r="F25">
+        <v>0.1342</v>
+      </c>
+      <c r="G25">
+        <v>0.03</v>
+      </c>
+      <c r="H25">
+        <v>0.5529061102831594</v>
+      </c>
+      <c r="I25">
+        <v>78282.023</v>
+      </c>
+      <c r="J25">
+        <v>0.687816557936147</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>2016</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TCH</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
         <v>496.2734</v>
       </c>
-      <c r="G8">
+      <c r="G26">
         <v>0.04</v>
       </c>
-      <c r="H8">
+      <c r="H26">
         <v>0</v>
       </c>
-      <c r="I8">
+      <c r="I26">
         <v>1181558597422.223</v>
       </c>
-      <c r="J8">
+      <c r="J26">
         <v>0.959412460905782</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>2016</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>V%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E27">
+        <v>0.0331</v>
+      </c>
+      <c r="F27">
+        <v>0.0551</v>
+      </c>
+      <c r="G27">
+        <v>0.03</v>
+      </c>
+      <c r="H27">
+        <v>0.6007259528130671</v>
+      </c>
+      <c r="I27">
+        <v>12848.3039</v>
+      </c>
+      <c r="J27">
+        <v>0.6370340249651866</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>2017</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ca</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E28">
+        <v>0.09379999999999999</v>
+      </c>
+      <c r="F28">
+        <v>0.2001</v>
+      </c>
+      <c r="G28">
+        <v>0.04</v>
+      </c>
+      <c r="H28">
+        <v>0.4687656171914042</v>
+      </c>
+      <c r="I28">
+        <v>73740.5129</v>
+      </c>
+      <c r="J28">
+        <v>0.8149125053113615</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>2017</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CTC</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E29">
+        <v>0.0333</v>
+      </c>
+      <c r="F29">
+        <v>0.0665</v>
+      </c>
+      <c r="G29">
+        <v>0.03</v>
+      </c>
+      <c r="H29">
+        <v>0.5007518796992482</v>
+      </c>
+      <c r="I29">
+        <v>8056.4678</v>
+      </c>
+      <c r="J29">
+        <v>0.8690200897661634</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>2017</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>H+Al</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E30">
+        <v>0.0292</v>
+      </c>
+      <c r="F30">
+        <v>0.0716</v>
+      </c>
+      <c r="G30">
+        <v>0.03</v>
+      </c>
+      <c r="H30">
+        <v>0.4078212290502793</v>
+      </c>
+      <c r="I30">
+        <v>13614.3205</v>
+      </c>
+      <c r="J30">
+        <v>0.6947393209911127</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>2017</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E31">
+        <v>0.0532</v>
+      </c>
+      <c r="F31">
+        <v>0.1822</v>
+      </c>
+      <c r="G31">
+        <v>0.02</v>
+      </c>
+      <c r="H31">
+        <v>0.29198682766191</v>
+      </c>
+      <c r="I31">
+        <v>124928.8021</v>
+      </c>
+      <c r="J31">
+        <v>0.6691255165554755</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>2017</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>m%</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E32">
+        <v>0.7032</v>
+      </c>
+      <c r="F32">
+        <v>1.0312</v>
+      </c>
+      <c r="G32">
+        <v>0.1</v>
+      </c>
+      <c r="H32">
+        <v>0.6819239720713732</v>
+      </c>
+      <c r="I32">
+        <v>5501167.458</v>
+      </c>
+      <c r="J32">
+        <v>0.8421247929243911</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>2017</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Mg</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E33">
+        <v>0.08169999999999999</v>
+      </c>
+      <c r="F33">
+        <v>0.1675</v>
+      </c>
+      <c r="G33">
+        <v>0.02</v>
+      </c>
+      <c r="H33">
+        <v>0.4877611940298507</v>
+      </c>
+      <c r="I33">
+        <v>56183.6503</v>
+      </c>
+      <c r="J33">
+        <v>0.7211286210533785</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>2017</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E34">
+        <v>0.0362</v>
+      </c>
+      <c r="F34">
+        <v>0.0584</v>
+      </c>
+      <c r="G34">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H34">
+        <v>0.6198630136986302</v>
+      </c>
+      <c r="I34">
+        <v>6591.3355</v>
+      </c>
+      <c r="J34">
+        <v>0.911616647728751</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>2017</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E35">
+        <v>0.1471</v>
+      </c>
+      <c r="F35">
+        <v>0.3595</v>
+      </c>
+      <c r="G35">
+        <v>0.03</v>
+      </c>
+      <c r="H35">
+        <v>0.4091794158553547</v>
+      </c>
+      <c r="I35">
+        <v>80572.17570000001</v>
+      </c>
+      <c r="J35">
+        <v>0.8663881763539096</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>2017</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E36">
+        <v>0.004</v>
+      </c>
+      <c r="F36">
+        <v>0.0081</v>
+      </c>
+      <c r="G36">
+        <v>0.09</v>
+      </c>
+      <c r="H36">
+        <v>0.4938271604938272</v>
+      </c>
+      <c r="I36">
+        <v>102.5183</v>
+      </c>
+      <c r="J36">
+        <v>0.8928921066979968</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>2017</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E37">
+        <v>0.1636</v>
+      </c>
+      <c r="F37">
+        <v>0.2821</v>
+      </c>
+      <c r="G37">
+        <v>0.02</v>
+      </c>
+      <c r="H37">
+        <v>0.5799361928394186</v>
+      </c>
+      <c r="I37">
+        <v>13160.9405</v>
+      </c>
+      <c r="J37">
+        <v>0.9561801573545348</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>2017</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E38">
+        <v>0.0747</v>
+      </c>
+      <c r="F38">
+        <v>0.1687</v>
+      </c>
+      <c r="G38">
+        <v>0.03</v>
+      </c>
+      <c r="H38">
+        <v>0.4427978660343806</v>
+      </c>
+      <c r="I38">
+        <v>66751.4391</v>
+      </c>
+      <c r="J38">
+        <v>0.7372737035476629</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>2017</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TCH</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0.1433</v>
+      </c>
+      <c r="G39">
+        <v>0.03</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>255814.4319</v>
+      </c>
+      <c r="J39">
+        <v>0.932540585141602</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>2017</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>V%</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E40">
+        <v>0.0213</v>
+      </c>
+      <c r="F40">
+        <v>0.0429</v>
+      </c>
+      <c r="G40">
+        <v>0.02</v>
+      </c>
+      <c r="H40">
+        <v>0.4965034965034965</v>
+      </c>
+      <c r="I40">
+        <v>7139.2655</v>
+      </c>
+      <c r="J40">
+        <v>0.461875382605981</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>2017</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ca</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E41">
+        <v>0.1072</v>
+      </c>
+      <c r="F41">
+        <v>0.2152</v>
+      </c>
+      <c r="G41">
+        <v>0.03</v>
+      </c>
+      <c r="H41">
+        <v>0.4981412639405205</v>
+      </c>
+      <c r="I41">
+        <v>40998.7426</v>
+      </c>
+      <c r="J41">
+        <v>0.9413288147208564</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>2017</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CTC</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E42">
+        <v>0.0316</v>
+      </c>
+      <c r="F42">
+        <v>0.0643</v>
+      </c>
+      <c r="G42">
+        <v>0.02</v>
+      </c>
+      <c r="H42">
+        <v>0.4914463452566097</v>
+      </c>
+      <c r="I42">
+        <v>3154.145</v>
+      </c>
+      <c r="J42">
+        <v>0.940625330217812</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>2017</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>H+Al</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E43">
+        <v>0.0348</v>
+      </c>
+      <c r="F43">
+        <v>0.0835</v>
+      </c>
+      <c r="G43">
+        <v>0.03</v>
+      </c>
+      <c r="H43">
+        <v>0.4167664670658682</v>
+      </c>
+      <c r="I43">
+        <v>6859.3851</v>
+      </c>
+      <c r="J43">
+        <v>0.9142829286033884</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>2017</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E44">
+        <v>0.0543</v>
+      </c>
+      <c r="F44">
+        <v>0.1847</v>
+      </c>
+      <c r="G44">
+        <v>0.05</v>
+      </c>
+      <c r="H44">
+        <v>0.2939902544667027</v>
+      </c>
+      <c r="I44">
+        <v>71093.02370000001</v>
+      </c>
+      <c r="J44">
+        <v>0.9222199881640192</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>2017</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>m%</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E45">
+        <v>0.7819</v>
+      </c>
+      <c r="F45">
+        <v>1.4307</v>
+      </c>
+      <c r="G45">
+        <v>0.02</v>
+      </c>
+      <c r="H45">
+        <v>0.546515691619487</v>
+      </c>
+      <c r="I45">
+        <v>732579.7259</v>
+      </c>
+      <c r="J45">
+        <v>0.9569241427797796</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>2017</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Mg</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E46">
+        <v>0.1025</v>
+      </c>
+      <c r="F46">
+        <v>0.1895</v>
+      </c>
+      <c r="G46">
+        <v>0.02</v>
+      </c>
+      <c r="H46">
+        <v>0.5408970976253298</v>
+      </c>
+      <c r="I46">
+        <v>21408.1544</v>
+      </c>
+      <c r="J46">
+        <v>0.953552651533834</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>2017</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E47">
+        <v>0.0273</v>
+      </c>
+      <c r="F47">
+        <v>0.0508</v>
+      </c>
+      <c r="G47">
+        <v>0.03</v>
+      </c>
+      <c r="H47">
+        <v>0.5374015748031497</v>
+      </c>
+      <c r="I47">
+        <v>2547.5534</v>
+      </c>
+      <c r="J47">
+        <v>0.9541547766757906</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>2017</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E48">
+        <v>0.1164</v>
+      </c>
+      <c r="F48">
+        <v>0.2437</v>
+      </c>
+      <c r="G48">
+        <v>0.03</v>
+      </c>
+      <c r="H48">
+        <v>0.4776364382437423</v>
+      </c>
+      <c r="I48">
+        <v>26030.3334</v>
+      </c>
+      <c r="J48">
+        <v>0.9513114354645</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>2017</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E49">
+        <v>0.0047</v>
+      </c>
+      <c r="F49">
+        <v>0.0083</v>
+      </c>
+      <c r="G49">
+        <v>0.02</v>
+      </c>
+      <c r="H49">
+        <v>0.5662650602409639</v>
+      </c>
+      <c r="I49">
+        <v>39.0748</v>
+      </c>
+      <c r="J49">
+        <v>0.8902024202440951</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>2017</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E50">
+        <v>0.1218</v>
+      </c>
+      <c r="F50">
+        <v>0.3089</v>
+      </c>
+      <c r="G50">
+        <v>0.03</v>
+      </c>
+      <c r="H50">
+        <v>0.3943023632243445</v>
+      </c>
+      <c r="I50">
+        <v>36700.9983</v>
+      </c>
+      <c r="J50">
+        <v>0.9762324005057388</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>2017</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E51">
+        <v>0.1075</v>
+      </c>
+      <c r="F51">
+        <v>0.1948</v>
+      </c>
+      <c r="G51">
+        <v>0.02</v>
+      </c>
+      <c r="H51">
+        <v>0.5518480492813141</v>
+      </c>
+      <c r="I51">
+        <v>22225.3628</v>
+      </c>
+      <c r="J51">
+        <v>0.9319607898549443</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>2017</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TCH</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0.1378</v>
+      </c>
+      <c r="G52">
+        <v>0.05</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>610201.7092</v>
+      </c>
+      <c r="J52">
+        <v>0.8079465352584415</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>2017</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>V%</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E53">
+        <v>0.0383</v>
+      </c>
+      <c r="F53">
+        <v>0.077</v>
+      </c>
+      <c r="G53">
+        <v>0.03</v>
+      </c>
+      <c r="H53">
+        <v>0.4974025974025974</v>
+      </c>
+      <c r="I53">
+        <v>4418.8727</v>
+      </c>
+      <c r="J53">
+        <v>0.952930310611358</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>2018</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ca</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E54">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="F54">
+        <v>0.1562</v>
+      </c>
+      <c r="G54">
+        <v>0.05</v>
+      </c>
+      <c r="H54">
+        <v>0.6126760563380281</v>
+      </c>
+      <c r="I54">
+        <v>28955.7881</v>
+      </c>
+      <c r="J54">
+        <v>0.8205377172279059</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>2018</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CTC</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E55">
+        <v>0.0279</v>
+      </c>
+      <c r="F55">
+        <v>0.0457</v>
+      </c>
+      <c r="G55">
+        <v>0.02</v>
+      </c>
+      <c r="H55">
+        <v>0.6105032822757113</v>
+      </c>
+      <c r="I55">
+        <v>236.9159</v>
+      </c>
+      <c r="J55">
+        <v>0.9585476682452242</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>2018</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>H+Al</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E56">
+        <v>0.0429</v>
+      </c>
+      <c r="F56">
+        <v>0.0735</v>
+      </c>
+      <c r="G56">
+        <v>0.03</v>
+      </c>
+      <c r="H56">
+        <v>0.5836734693877551</v>
+      </c>
+      <c r="I56">
+        <v>5668.8198</v>
+      </c>
+      <c r="J56">
+        <v>0.675220796621865</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>2018</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Gau</t>
+        </is>
+      </c>
+      <c r="E57">
+        <v>0.0742</v>
+      </c>
+      <c r="F57">
+        <v>0.1436</v>
+      </c>
+      <c r="G57">
+        <v>0.03</v>
+      </c>
+      <c r="H57">
+        <v>0.5167130919220055</v>
+      </c>
+      <c r="I57">
+        <v>21826.2243</v>
+      </c>
+      <c r="J57">
+        <v>0.6511984679005346</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>2018</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>m%</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E58">
+        <v>0.93</v>
+      </c>
+      <c r="F58">
+        <v>1.2241</v>
+      </c>
+      <c r="G58">
+        <v>0.12</v>
+      </c>
+      <c r="H58">
+        <v>0.7597418511559514</v>
+      </c>
+      <c r="I58">
+        <v>4489061.8724</v>
+      </c>
+      <c r="J58">
+        <v>0.8215872059307464</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>2018</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Mg</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E59">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="F59">
+        <v>0.1306</v>
+      </c>
+      <c r="G59">
+        <v>0.04</v>
+      </c>
+      <c r="H59">
+        <v>0.6508422664624809</v>
+      </c>
+      <c r="I59">
+        <v>8680.794599999999</v>
+      </c>
+      <c r="J59">
+        <v>0.8442108833621332</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>2018</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E60">
+        <v>0.0315</v>
+      </c>
+      <c r="F60">
+        <v>0.0569</v>
+      </c>
+      <c r="G60">
+        <v>0.03</v>
+      </c>
+      <c r="H60">
+        <v>0.5536028119507909</v>
+      </c>
+      <c r="I60">
+        <v>1122.4004</v>
+      </c>
+      <c r="J60">
+        <v>0.9359891801830692</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>2018</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Gau</t>
+        </is>
+      </c>
+      <c r="E61">
+        <v>0.1058</v>
+      </c>
+      <c r="F61">
+        <v>0.1857</v>
+      </c>
+      <c r="G61">
+        <v>0.03</v>
+      </c>
+      <c r="H61">
+        <v>0.5697361335487345</v>
+      </c>
+      <c r="I61">
+        <v>89961.1145</v>
+      </c>
+      <c r="J61">
+        <v>0.1485152072746604</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>2018</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Gau</t>
+        </is>
+      </c>
+      <c r="E62">
+        <v>0.005</v>
+      </c>
+      <c r="F62">
+        <v>0.0075</v>
+      </c>
+      <c r="G62">
+        <v>0.03</v>
+      </c>
+      <c r="H62">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="I62">
+        <v>142.9337</v>
+      </c>
+      <c r="J62">
+        <v>0.4792950871224653</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>2018</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E63">
+        <v>0.196</v>
+      </c>
+      <c r="F63">
+        <v>0.3951</v>
+      </c>
+      <c r="G63">
+        <v>0.03</v>
+      </c>
+      <c r="H63">
+        <v>0.4960769425461909</v>
+      </c>
+      <c r="I63">
+        <v>113777.2606</v>
+      </c>
+      <c r="J63">
+        <v>0.911801721904874</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>2018</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E64">
+        <v>0.0838</v>
+      </c>
+      <c r="F64">
+        <v>0.1338</v>
+      </c>
+      <c r="G64">
+        <v>0.05</v>
+      </c>
+      <c r="H64">
+        <v>0.6263079222720478</v>
+      </c>
+      <c r="I64">
+        <v>15527.9343</v>
+      </c>
+      <c r="J64">
+        <v>0.8227313188149711</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>2018</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>TCH</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Gau</t>
+        </is>
+      </c>
+      <c r="E65">
+        <v>0.0206</v>
+      </c>
+      <c r="F65">
+        <v>0.1762</v>
+      </c>
+      <c r="G65">
+        <v>0.02</v>
+      </c>
+      <c r="H65">
+        <v>0.1169125993189557</v>
+      </c>
+      <c r="I65">
+        <v>31813.3296</v>
+      </c>
+      <c r="J65">
+        <v>0.8347819317723106</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>2018</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>V%</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E66">
+        <v>0.041</v>
+      </c>
+      <c r="F66">
+        <v>0.0702</v>
+      </c>
+      <c r="G66">
+        <v>0.29</v>
+      </c>
+      <c r="H66">
+        <v>0.584045584045584</v>
+      </c>
+      <c r="I66">
+        <v>1516.229</v>
+      </c>
+      <c r="J66">
+        <v>0.953621505530341</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>2018</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ca</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E67">
+        <v>0.0867</v>
+      </c>
+      <c r="F67">
+        <v>0.1702</v>
+      </c>
+      <c r="G67">
+        <v>0.02</v>
+      </c>
+      <c r="H67">
+        <v>0.509400705052879</v>
+      </c>
+      <c r="I67">
+        <v>32495.4167</v>
+      </c>
+      <c r="J67">
+        <v>0.8762113721517721</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>2018</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CTC</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E68">
+        <v>0.0135</v>
+      </c>
+      <c r="F68">
+        <v>0.0468</v>
+      </c>
+      <c r="G68">
+        <v>0.02</v>
+      </c>
+      <c r="H68">
+        <v>0.2884615384615384</v>
+      </c>
+      <c r="I68">
+        <v>3324.7764</v>
+      </c>
+      <c r="J68">
+        <v>0.8435978675080463</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>2018</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>H+Al</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E69">
+        <v>0.0452</v>
+      </c>
+      <c r="F69">
+        <v>0.0713</v>
+      </c>
+      <c r="G69">
+        <v>0.02</v>
+      </c>
+      <c r="H69">
+        <v>0.6339410939691444</v>
+      </c>
+      <c r="I69">
+        <v>2118.519</v>
+      </c>
+      <c r="J69">
+        <v>0.8412174713597523</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>2018</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Gau</t>
+        </is>
+      </c>
+      <c r="E70">
+        <v>0.0599</v>
+      </c>
+      <c r="F70">
+        <v>0.1186</v>
+      </c>
+      <c r="G70">
+        <v>0.03</v>
+      </c>
+      <c r="H70">
+        <v>0.5050590219224284</v>
+      </c>
+      <c r="I70">
+        <v>77694.4748</v>
+      </c>
+      <c r="J70">
+        <v>0.6619138449991012</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>2018</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>m%</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E71">
+        <v>0.0309</v>
+      </c>
+      <c r="F71">
+        <v>1.3508</v>
+      </c>
+      <c r="G71">
+        <v>0.01</v>
+      </c>
+      <c r="H71">
+        <v>0.02287533313591945</v>
+      </c>
+      <c r="I71">
+        <v>278273.3281</v>
+      </c>
+      <c r="J71">
+        <v>0.7293938985074767</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>2018</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Mg</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E72">
+        <v>0.0429</v>
+      </c>
+      <c r="F72">
+        <v>0.1369</v>
+      </c>
+      <c r="G72">
+        <v>0.02</v>
+      </c>
+      <c r="H72">
+        <v>0.3133674214755296</v>
+      </c>
+      <c r="I72">
+        <v>7932.5327</v>
+      </c>
+      <c r="J72">
+        <v>0.862914751896795</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>2018</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E73">
+        <v>0.0326</v>
+      </c>
+      <c r="F73">
+        <v>0.056</v>
+      </c>
+      <c r="G73">
+        <v>0.03</v>
+      </c>
+      <c r="H73">
+        <v>0.5821428571428571</v>
+      </c>
+      <c r="I73">
+        <v>7354.8155</v>
+      </c>
+      <c r="J73">
+        <v>0.8609201357325725</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>2018</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E74">
+        <v>0.0495</v>
+      </c>
+      <c r="F74">
+        <v>0.1117</v>
+      </c>
+      <c r="G74">
+        <v>0.02</v>
+      </c>
+      <c r="H74">
+        <v>0.4431512981199642</v>
+      </c>
+      <c r="I74">
+        <v>12396.0523</v>
+      </c>
+      <c r="J74">
+        <v>0.9070915063392878</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>2018</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E75">
+        <v>0.004</v>
+      </c>
+      <c r="F75">
+        <v>0.007</v>
+      </c>
+      <c r="G75">
+        <v>0.02</v>
+      </c>
+      <c r="H75">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="I75">
+        <v>35.4108</v>
+      </c>
+      <c r="J75">
+        <v>0.8965974933280045</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>2018</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E76">
+        <v>0.1524</v>
+      </c>
+      <c r="F76">
+        <v>0.3127</v>
+      </c>
+      <c r="G76">
+        <v>0.02</v>
+      </c>
+      <c r="H76">
+        <v>0.4873680844259675</v>
+      </c>
+      <c r="I76">
+        <v>12251.816</v>
+      </c>
+      <c r="J76">
+        <v>0.9256815042752732</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>2018</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="E77">
+        <v>0.0394</v>
+      </c>
+      <c r="F77">
+        <v>0.1494</v>
+      </c>
+      <c r="G77">
+        <v>0.02</v>
+      </c>
+      <c r="H77">
+        <v>0.2637215528781793</v>
+      </c>
+      <c r="I77">
+        <v>15746.6753</v>
+      </c>
+      <c r="J77">
+        <v>0.8399511564207341</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>2018</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>TCH</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E78">
+        <v>0.0045</v>
+      </c>
+      <c r="F78">
+        <v>0.1249</v>
+      </c>
+      <c r="G78">
+        <v>0.03</v>
+      </c>
+      <c r="H78">
+        <v>0.03602882305844675</v>
+      </c>
+      <c r="I78">
+        <v>46346.0677</v>
+      </c>
+      <c r="J78">
+        <v>0.9610902524425776</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>2018</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>POT</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>V%</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Sph</t>
+        </is>
+      </c>
+      <c r="E79">
+        <v>0.0417</v>
+      </c>
+      <c r="F79">
+        <v>0.0722</v>
+      </c>
+      <c r="G79">
+        <v>0.01</v>
+      </c>
+      <c r="H79">
+        <v>0.5775623268698061</v>
+      </c>
+      <c r="I79">
+        <v>3939.4219</v>
+      </c>
+      <c r="J79">
+        <v>0.6698855091339107</v>
       </c>
     </row>
   </sheetData>

--- a/output/semivariogram-models.xlsx
+++ b/output/semivariogram-models.xlsx
@@ -464,22 +464,22 @@
         </is>
       </c>
       <c r="E3">
-        <v>0.9293</v>
+        <v>0.9474</v>
       </c>
       <c r="F3">
-        <v>1.1993</v>
+        <v>1.3542</v>
       </c>
       <c r="G3">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="H3">
-        <v>0.7748686733928125</v>
+        <v>0.6996012405848471</v>
       </c>
       <c r="I3">
-        <v>4473312.4705</v>
+        <v>3423748.4271</v>
       </c>
       <c r="J3">
-        <v>0.7819879542168291</v>
+        <v>0.6552464926469308</v>
       </c>
     </row>
     <row r="4">
@@ -502,22 +502,22 @@
         </is>
       </c>
       <c r="E4">
-        <v>0.9286</v>
+        <v>0.8292</v>
       </c>
       <c r="F4">
-        <v>1.3507</v>
+        <v>1.3426</v>
       </c>
       <c r="G4">
         <v>0.01</v>
       </c>
       <c r="H4">
-        <v>0.687495372769675</v>
+        <v>0.6176076269924028</v>
       </c>
       <c r="I4">
-        <v>276762.2066</v>
+        <v>476385.6177</v>
       </c>
       <c r="J4">
-        <v>0.7731585752263095</v>
+        <v>0.9568094887959168</v>
       </c>
     </row>
   </sheetData>
